--- a/artfynd/A 18951-2024 artfynd.xlsx
+++ b/artfynd/A 18951-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,118 +897,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>106280422</v>
-      </c>
-      <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Jämtland, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>479040.5244491342</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7007713.864779843</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Frösö</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2022-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
